--- a/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_16_6.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_16_6.xlsx
@@ -517,657 +517,657 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9994304030968046</v>
+        <v>0.9996968805094114</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6591870217860774</v>
+        <v>0.6440890151240956</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9998701892230342</v>
+        <v>0.9999319752765347</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9995860352865759</v>
+        <v>0.9999285009628428</v>
       </c>
       <c r="F2" t="n">
-        <v>0.999868291402217</v>
+        <v>0.9999299379995111</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0003381373270418123</v>
+        <v>0.0001799448236935998</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2023213062218625</v>
+        <v>0.2112841351763431</v>
       </c>
       <c r="I2" t="n">
-        <v>6.416432972351377e-05</v>
+        <v>1.712181559257334e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001227284268548533</v>
+        <v>8.971354901380105e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>9.344632405608992e-05</v>
+        <v>5.341768230318719e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005301251801805545</v>
+        <v>0.004178638278363877</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01838851073474446</v>
+        <v>0.01341435140786165</v>
       </c>
       <c r="N2" t="n">
-        <v>1.000506308358396</v>
+        <v>1.00026943954719</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01917134770618736</v>
+        <v>0.01398542811882984</v>
       </c>
       <c r="P2" t="n">
-        <v>117.9841169039456</v>
+        <v>119.2457205782022</v>
       </c>
       <c r="Q2" t="n">
-        <v>180.1467839722239</v>
+        <v>181.4083876464804</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_16_6_1</t>
+          <t>model_16_6_22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9994907651996179</v>
+        <v>0.9996968805094114</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6588690978810228</v>
+        <v>0.6440890151240956</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9998926155539886</v>
+        <v>0.9999319752765347</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9996715695951198</v>
+        <v>0.9999285009628428</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9998939741448157</v>
+        <v>0.9999299379995111</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0003023037753047684</v>
+        <v>0.0001799448236935998</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2025100395855005</v>
+        <v>0.2112841351763431</v>
       </c>
       <c r="I3" t="n">
-        <v>5.307919081993554e-05</v>
+        <v>1.712181559257334e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>9.737000670623639e-05</v>
+        <v>8.971354901380105e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>7.522459876308597e-05</v>
+        <v>5.341768230318719e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005079913953737005</v>
+        <v>0.004178638278363877</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01738688515245811</v>
+        <v>0.01341435140786165</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000452653155895</v>
+        <v>1.00026943954719</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01812708084921228</v>
+        <v>0.01398542811882984</v>
       </c>
       <c r="P3" t="n">
-        <v>118.2081563353072</v>
+        <v>119.2457205782022</v>
       </c>
       <c r="Q3" t="n">
-        <v>180.3708234035854</v>
+        <v>181.4083876464804</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_16_6_2</t>
+          <t>model_16_6_21</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.999543718079839</v>
+        <v>0.9996968805094114</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6585683129808502</v>
+        <v>0.6440890151240956</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9999103159693172</v>
+        <v>0.9999319752765347</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9997334802986876</v>
+        <v>0.9999285009628428</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9999130750195231</v>
+        <v>0.9999299379995111</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0002708686581601896</v>
+        <v>0.0001799448236935998</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2026885984954741</v>
+        <v>0.2112841351763431</v>
       </c>
       <c r="I4" t="n">
-        <v>4.433003060429315e-05</v>
+        <v>1.712181559257334e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>7.901529431661096e-05</v>
+        <v>8.971354901380105e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>6.167266246045206e-05</v>
+        <v>5.341768230318719e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004867560304606789</v>
+        <v>0.004178638278363877</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01645808792539977</v>
+        <v>0.01341435140786165</v>
       </c>
       <c r="N4" t="n">
-        <v>1.000405583929032</v>
+        <v>1.00026943954719</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01715874280132275</v>
+        <v>0.01398542811882984</v>
       </c>
       <c r="P4" t="n">
-        <v>118.4277530216077</v>
+        <v>119.2457205782022</v>
       </c>
       <c r="Q4" t="n">
-        <v>180.5904200898859</v>
+        <v>181.4083876464804</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_16_6_3</t>
+          <t>model_16_6_20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9995900718329531</v>
+        <v>0.9996968805094114</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6582811168933294</v>
+        <v>0.6440890151240956</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9999237707097643</v>
+        <v>0.9999319752765347</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9997754104631636</v>
+        <v>0.9999285009628428</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9999265223884511</v>
+        <v>0.9999299379995111</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002433510679338074</v>
+        <v>0.0001799448236935998</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2028590904992514</v>
+        <v>0.2112841351763431</v>
       </c>
       <c r="I5" t="n">
-        <v>3.767947028431524e-05</v>
+        <v>1.712181559257334e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>6.658422723037231e-05</v>
+        <v>8.971354901380105e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.213184875734377e-05</v>
+        <v>5.341768230318719e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004663973670805225</v>
+        <v>0.004178638278363877</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01559971371320023</v>
+        <v>0.01341435140786165</v>
       </c>
       <c r="N5" t="n">
-        <v>1.000364380592931</v>
+        <v>1.00026943954719</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0162638258218303</v>
+        <v>0.01398542811882984</v>
       </c>
       <c r="P5" t="n">
-        <v>118.6420108664519</v>
+        <v>119.2457205782022</v>
       </c>
       <c r="Q5" t="n">
-        <v>180.8046779347301</v>
+        <v>181.4083876464804</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_16_6_4</t>
+          <t>model_16_6_19</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9996305841930888</v>
+        <v>0.9996968805094114</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6580060943896178</v>
+        <v>0.6440890151240956</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9999334911313105</v>
+        <v>0.9999319752765347</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9998005913531873</v>
+        <v>0.9999285009628428</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9999351691408476</v>
+        <v>0.9999299379995111</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0002193011809144232</v>
+        <v>0.0001799448236935998</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2030223557378082</v>
+        <v>0.2112841351763431</v>
       </c>
       <c r="I6" t="n">
-        <v>3.287475107906836e-05</v>
+        <v>1.712181559257334e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>5.911883001366657e-05</v>
+        <v>8.971354901380105e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>4.599703872920623e-05</v>
+        <v>5.341768230318719e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004469072132555162</v>
+        <v>0.004178638278363877</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01480882105079345</v>
+        <v>0.01341435140786165</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000328369606143</v>
+        <v>1.00026943954719</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01543926322141135</v>
+        <v>0.01398542811882984</v>
       </c>
       <c r="P6" t="n">
-        <v>118.8501290352565</v>
+        <v>119.2457205782022</v>
       </c>
       <c r="Q6" t="n">
-        <v>181.0127961035347</v>
+        <v>181.4083876464804</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_16_6_5</t>
+          <t>model_16_6_18</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9996659136956826</v>
+        <v>0.9996968805094114</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6577415626993532</v>
+        <v>0.6440890151240956</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9999398888521537</v>
+        <v>0.9999319752765347</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9998117392761822</v>
+        <v>0.9999285009628428</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9999397276379408</v>
+        <v>0.9999299379995111</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001983280620197458</v>
+        <v>0.0001799448236935998</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2031793931763232</v>
+        <v>0.2112841351763431</v>
       </c>
       <c r="I7" t="n">
-        <v>2.97124137196021e-05</v>
+        <v>1.712181559257334e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>5.581379698188007e-05</v>
+        <v>8.971354901380105e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>4.276281709329204e-05</v>
+        <v>5.341768230318719e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004282455237480985</v>
+        <v>0.004178638278363877</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01408289963110388</v>
+        <v>0.01341435140786165</v>
       </c>
       <c r="N7" t="n">
-        <v>1.000296965603838</v>
+        <v>1.00026943954719</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0146824378240211</v>
+        <v>0.01398542811882984</v>
       </c>
       <c r="P7" t="n">
-        <v>119.0511760389833</v>
+        <v>119.2457205782022</v>
       </c>
       <c r="Q7" t="n">
-        <v>181.2138431072616</v>
+        <v>181.4083876464804</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_16_6_6</t>
+          <t>model_16_6_17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9996966420285334</v>
+        <v>0.9996968805094114</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6574865065114011</v>
+        <v>0.6440890151240956</v>
       </c>
       <c r="D8" t="n">
-        <v>0.99994336007805</v>
+        <v>0.9999319752765347</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9998111390044535</v>
+        <v>0.9999285009628428</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9999408114459262</v>
+        <v>0.9999299379995111</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0001800863962446575</v>
+        <v>0.0001799448236935998</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2033308055473453</v>
+        <v>0.2112841351763431</v>
       </c>
       <c r="I8" t="n">
-        <v>2.799661717203319e-05</v>
+        <v>1.712181559257334e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>5.599175998828227e-05</v>
+        <v>8.971354901380105e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>4.199386294816078e-05</v>
+        <v>5.341768230318719e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004103987923603889</v>
+        <v>0.004178638278363877</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01341962727666672</v>
+        <v>0.01341435140786165</v>
       </c>
       <c r="N8" t="n">
-        <v>1.000269651530193</v>
+        <v>1.00026943954719</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0139909285922925</v>
+        <v>0.01398542811882984</v>
       </c>
       <c r="P8" t="n">
-        <v>119.2441476861804</v>
+        <v>119.2457205782022</v>
       </c>
       <c r="Q8" t="n">
-        <v>181.4068147544587</v>
+        <v>181.4083876464804</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_16_6_7</t>
+          <t>model_16_6_16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9997232981140466</v>
+        <v>0.9996968805094114</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6572402296019797</v>
+        <v>0.6440890151240956</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9999442596258397</v>
+        <v>0.9999319752765347</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9998007422294016</v>
+        <v>0.9999285009628428</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9999389521235433</v>
+        <v>0.9999299379995111</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001642621924010291</v>
+        <v>0.0001799448236935998</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2034770061593864</v>
+        <v>0.2112841351763431</v>
       </c>
       <c r="I9" t="n">
-        <v>2.755197858091784e-05</v>
+        <v>1.712181559257334e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>5.907409963004623e-05</v>
+        <v>8.971354901380105e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.331303910548204e-05</v>
+        <v>5.341768230318719e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003933505235144194</v>
+        <v>0.004178638278363877</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01281648128001711</v>
+        <v>0.01341435140786165</v>
       </c>
       <c r="N9" t="n">
-        <v>1.000245957231959</v>
+        <v>1.00026943954719</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01336210542188118</v>
+        <v>0.01398542811882984</v>
       </c>
       <c r="P9" t="n">
-        <v>119.4280933452049</v>
+        <v>119.2457205782022</v>
       </c>
       <c r="Q9" t="n">
-        <v>181.5907604134831</v>
+        <v>181.4083876464804</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_16_6_8</t>
+          <t>model_16_6_15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9997463347734811</v>
+        <v>0.9996968805094114</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6570023941201335</v>
+        <v>0.6440890151240956</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9999429243751629</v>
+        <v>0.9999319752765347</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9997822111245042</v>
+        <v>0.9999285009628428</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9999346152707133</v>
+        <v>0.9999299379995111</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0001505866362288785</v>
+        <v>0.0001799448236935998</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2036181955753682</v>
+        <v>0.2112841351763431</v>
       </c>
       <c r="I10" t="n">
-        <v>2.821198129173493e-05</v>
+        <v>1.712181559257334e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>6.456803009850722e-05</v>
+        <v>8.971354901380105e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>4.639000569512107e-05</v>
+        <v>5.341768230318719e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>0.003773876112123851</v>
+        <v>0.004178638278363877</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01227137466744776</v>
+        <v>0.01341435140786165</v>
       </c>
       <c r="N10" t="n">
-        <v>1.00022548020135</v>
+        <v>1.00026943954719</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0127937924922885</v>
+        <v>0.01398542811882984</v>
       </c>
       <c r="P10" t="n">
-        <v>119.6019439667917</v>
+        <v>119.2457205782022</v>
       </c>
       <c r="Q10" t="n">
-        <v>181.76461103507</v>
+        <v>181.4083876464804</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_16_6_9</t>
+          <t>model_16_6_14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9997661681295796</v>
+        <v>0.9996968805094114</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6567725319399174</v>
+        <v>0.6440890151240956</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9999396611609624</v>
+        <v>0.9999319752765347</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9997569429469144</v>
+        <v>0.9999285009628428</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9999281979604345</v>
+        <v>0.9999299379995111</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0001388126992923909</v>
+        <v>0.0001799448236935998</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2037546516950736</v>
+        <v>0.2112841351763431</v>
       </c>
       <c r="I11" t="n">
-        <v>2.982495948049972e-05</v>
+        <v>1.712181559257334e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>7.205930552494017e-05</v>
+        <v>8.971354901380105e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>5.094304221643363e-05</v>
+        <v>5.341768230318719e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>0.003623712004529587</v>
+        <v>0.004178638278363877</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01178188012553136</v>
+        <v>0.01341435140786165</v>
       </c>
       <c r="N11" t="n">
-        <v>1.000207850551485</v>
+        <v>1.00026943954719</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01228345915432933</v>
+        <v>0.01398542811882984</v>
       </c>
       <c r="P11" t="n">
-        <v>119.7647700412316</v>
+        <v>119.2457205782022</v>
       </c>
       <c r="Q11" t="n">
-        <v>181.9274371095099</v>
+        <v>181.4083876464804</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_16_6_10</t>
+          <t>model_16_6_13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9997831716458485</v>
+        <v>0.9996968805094114</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6565507428516204</v>
+        <v>0.6440890151240956</v>
       </c>
       <c r="D12" t="n">
-        <v>0.99993473052521</v>
+        <v>0.9999319752765347</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9997261545139648</v>
+        <v>0.9999285009628428</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9999200476563093</v>
+        <v>0.9999299379995111</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0001287186775215499</v>
+        <v>0.0001799448236935998</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2038863152786764</v>
+        <v>0.2112841351763431</v>
       </c>
       <c r="I12" t="n">
-        <v>3.226212953340932e-05</v>
+        <v>1.712181559257334e-05</v>
       </c>
       <c r="J12" t="n">
-        <v>8.118717516864904e-05</v>
+        <v>8.971354901380105e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>5.672562568673942e-05</v>
+        <v>5.341768230318719e-05</v>
       </c>
       <c r="L12" t="n">
-        <v>0.003480720745579285</v>
+        <v>0.004178638278363877</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01134542540064276</v>
+        <v>0.01341435140786165</v>
       </c>
       <c r="N12" t="n">
-        <v>1.000192736314801</v>
+        <v>1.00026943954719</v>
       </c>
       <c r="O12" t="n">
-        <v>0.01182842364821639</v>
+        <v>0.01398542811882984</v>
       </c>
       <c r="P12" t="n">
-        <v>119.9157626588083</v>
+        <v>119.2457205782022</v>
       </c>
       <c r="Q12" t="n">
-        <v>182.0784297270866</v>
+        <v>181.4083876464804</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_16_6_11</t>
+          <t>model_16_6_23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9997976654183207</v>
+        <v>0.9996968805094114</v>
       </c>
       <c r="C13" t="n">
-        <v>0.65633646150761</v>
+        <v>0.6440890151240956</v>
       </c>
       <c r="D13" t="n">
-        <v>0.999928376580146</v>
+        <v>0.9999319752765347</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9996908612513226</v>
+        <v>0.9999285009628428</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9999104624924922</v>
+        <v>0.9999299379995111</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0001201145480836272</v>
+        <v>0.0001799448236935998</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2040135219409531</v>
+        <v>0.2112841351763431</v>
       </c>
       <c r="I13" t="n">
-        <v>3.540282890877064e-05</v>
+        <v>1.712181559257334e-05</v>
       </c>
       <c r="J13" t="n">
-        <v>9.165059502592074e-05</v>
+        <v>8.971354901380105e-05</v>
       </c>
       <c r="K13" t="n">
-        <v>6.352623201967738e-05</v>
+        <v>5.341768230318719e-05</v>
       </c>
       <c r="L13" t="n">
-        <v>0.003375977681805117</v>
+        <v>0.004178638278363877</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01095967828376487</v>
+        <v>0.01341435140786165</v>
       </c>
       <c r="N13" t="n">
-        <v>1.000179852961493</v>
+        <v>1.00026943954719</v>
       </c>
       <c r="O13" t="n">
-        <v>0.01142625447796639</v>
+        <v>0.01398542811882984</v>
       </c>
       <c r="P13" t="n">
-        <v>120.0541294062567</v>
+        <v>119.2457205782022</v>
       </c>
       <c r="Q13" t="n">
-        <v>182.216796474535</v>
+        <v>181.4083876464804</v>
       </c>
     </row>
     <row r="14">
@@ -1177,657 +1177,657 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9998099403007048</v>
+        <v>0.9996968805094114</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6561296433057077</v>
+        <v>0.6440890151240956</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9999208401183468</v>
+        <v>0.9999319752765347</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9996519594363333</v>
+        <v>0.9999285009628428</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9998997087446311</v>
+        <v>0.9999299379995111</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0001128276476531118</v>
+        <v>0.0001799448236935998</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2041362981596835</v>
+        <v>0.2112841351763431</v>
       </c>
       <c r="I14" t="n">
-        <v>3.912803594579934e-05</v>
+        <v>1.712181559257334e-05</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0001031838450847027</v>
+        <v>8.971354901380105e-05</v>
       </c>
       <c r="K14" t="n">
-        <v>7.115594051525103e-05</v>
+        <v>5.341768230318719e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>0.003291161186194941</v>
+        <v>0.004178638278363877</v>
       </c>
       <c r="M14" t="n">
-        <v>0.01062203594670587</v>
+        <v>0.01341435140786165</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000168941954929</v>
+        <v>1.00026943954719</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0110742380076028</v>
+        <v>0.01398542811882984</v>
       </c>
       <c r="P14" t="n">
-        <v>120.179298291251</v>
+        <v>119.2457205782022</v>
       </c>
       <c r="Q14" t="n">
-        <v>182.3419653595292</v>
+        <v>181.4083876464804</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_16_6_13</t>
+          <t>model_16_6_10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9998202596818234</v>
+        <v>0.9996968805094114</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6559303074095961</v>
+        <v>0.6440890151240956</v>
       </c>
       <c r="D15" t="n">
-        <v>0.999912312809465</v>
+        <v>0.9999319752765347</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9996102096338239</v>
+        <v>0.9999285009628428</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9998880162326487</v>
+        <v>0.9999299379995111</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0001067016172470885</v>
+        <v>0.0001799448236935998</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2042546325584776</v>
+        <v>0.2112841351763431</v>
       </c>
       <c r="I15" t="n">
-        <v>4.334301001444193e-05</v>
+        <v>1.712181559257334e-05</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0001155614401244035</v>
+        <v>8.971354901380105e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>7.945169555429317e-05</v>
+        <v>5.341768230318719e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.003268970301323805</v>
+        <v>0.004178638278363877</v>
       </c>
       <c r="M15" t="n">
-        <v>0.01032964748900409</v>
+        <v>0.01341435140786165</v>
       </c>
       <c r="N15" t="n">
-        <v>1.000159769171713</v>
+        <v>1.00026943954719</v>
       </c>
       <c r="O15" t="n">
-        <v>0.01076940196792911</v>
+        <v>0.01398542811882984</v>
       </c>
       <c r="P15" t="n">
-        <v>120.2909484856331</v>
+        <v>119.2457205782022</v>
       </c>
       <c r="Q15" t="n">
-        <v>182.4536155539113</v>
+        <v>181.4083876464804</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_16_6_14</t>
+          <t>model_16_6_9</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9998288500485274</v>
+        <v>0.9996968805094114</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6557382175255102</v>
+        <v>0.6440890151240956</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9999029709144429</v>
+        <v>0.9999319752765347</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9995662428562583</v>
+        <v>0.9999285009628428</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9998755719138791</v>
+        <v>0.9999299379995111</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0001016020044870516</v>
+        <v>0.0001799448236935998</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2043686654115219</v>
+        <v>0.2112841351763431</v>
       </c>
       <c r="I16" t="n">
-        <v>4.796062687531034e-05</v>
+        <v>1.712181559257334e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0001285963034098914</v>
+        <v>8.971354901380105e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>8.828085222261984e-05</v>
+        <v>5.341768230318719e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>0.003273612154445902</v>
+        <v>0.004178638278363877</v>
       </c>
       <c r="M16" t="n">
-        <v>0.01007978196624568</v>
+        <v>0.01341435140786165</v>
       </c>
       <c r="N16" t="n">
-        <v>1.000152133290198</v>
+        <v>1.00026943954719</v>
       </c>
       <c r="O16" t="n">
-        <v>0.01050889915257393</v>
+        <v>0.01398542811882984</v>
       </c>
       <c r="P16" t="n">
-        <v>120.3888945876225</v>
+        <v>119.2457205782022</v>
       </c>
       <c r="Q16" t="n">
-        <v>182.5515616559007</v>
+        <v>181.4083876464804</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_16_6_15</t>
+          <t>model_16_6_8</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9998359253315859</v>
+        <v>0.9996968805094114</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6555531704612323</v>
+        <v>0.6440890151240956</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9998929708794306</v>
+        <v>0.9999319752765347</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9995206718418056</v>
+        <v>0.9999285009628428</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9998625706376626</v>
+        <v>0.9999299379995111</v>
       </c>
       <c r="G17" t="n">
-        <v>9.740181082720182e-05</v>
+        <v>0.0001799448236935998</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2044785173424943</v>
+        <v>0.2112841351763431</v>
       </c>
       <c r="I17" t="n">
-        <v>5.290355656710278e-05</v>
+        <v>1.712181559257334e-05</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0001421067759999265</v>
+        <v>8.971354901380105e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>9.750516628351461e-05</v>
+        <v>5.341768230318719e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>0.003277801951912422</v>
+        <v>0.004178638278363877</v>
       </c>
       <c r="M17" t="n">
-        <v>0.009869235574612749</v>
+        <v>0.01341435140786165</v>
       </c>
       <c r="N17" t="n">
-        <v>1.000145844149701</v>
+        <v>1.00026943954719</v>
       </c>
       <c r="O17" t="n">
-        <v>0.01028938936515807</v>
+        <v>0.01398542811882984</v>
       </c>
       <c r="P17" t="n">
-        <v>120.4733315116671</v>
+        <v>119.2457205782022</v>
       </c>
       <c r="Q17" t="n">
-        <v>182.6359985799454</v>
+        <v>181.4083876464804</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_16_6_16</t>
+          <t>model_16_6_7</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9998416578511964</v>
+        <v>0.9996968805094114</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6553751936415964</v>
+        <v>0.6440890151240956</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9998824554684929</v>
+        <v>0.9999319752765347</v>
       </c>
       <c r="E18" t="n">
-        <v>0.999473886668542</v>
+        <v>0.9999285009628428</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9998491327943774</v>
+        <v>0.9999299379995111</v>
       </c>
       <c r="G18" t="n">
-        <v>9.399873955449664e-05</v>
+        <v>0.0001799448236935998</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2045841720708285</v>
+        <v>0.2112841351763431</v>
       </c>
       <c r="I18" t="n">
-        <v>5.810123206337183e-05</v>
+        <v>1.712181559257334e-05</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0001559772111567628</v>
+        <v>8.971354901380105e-05</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0001070392216100673</v>
+        <v>5.341768230318719e-05</v>
       </c>
       <c r="L18" t="n">
-        <v>0.003281679990194222</v>
+        <v>0.004178638278363877</v>
       </c>
       <c r="M18" t="n">
-        <v>0.009695294712101156</v>
+        <v>0.01341435140786165</v>
       </c>
       <c r="N18" t="n">
-        <v>1.000140748576714</v>
+        <v>1.00026943954719</v>
       </c>
       <c r="O18" t="n">
-        <v>0.01010804348002214</v>
+        <v>0.01398542811882984</v>
       </c>
       <c r="P18" t="n">
-        <v>120.5444583695578</v>
+        <v>119.2457205782022</v>
       </c>
       <c r="Q18" t="n">
-        <v>182.707125437836</v>
+        <v>181.4083876464804</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_16_6_17</t>
+          <t>model_16_6_6</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9998462231207559</v>
+        <v>0.9996968805094114</v>
       </c>
       <c r="C19" t="n">
-        <v>0.655204129812237</v>
+        <v>0.6440890151240956</v>
       </c>
       <c r="D19" t="n">
-        <v>0.999871556734731</v>
+        <v>0.9999319752765347</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9994263846908138</v>
+        <v>0.9999285009628428</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9998354116609931</v>
+        <v>0.9999299379995111</v>
       </c>
       <c r="G19" t="n">
-        <v>9.128859833460403e-05</v>
+        <v>0.0001799448236935998</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2046857229495088</v>
+        <v>0.2112841351763431</v>
       </c>
       <c r="I19" t="n">
-        <v>6.34883806731156e-05</v>
+        <v>1.712181559257334e-05</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0001700601578670286</v>
+        <v>8.971354901380105e-05</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0001167742692700721</v>
+        <v>5.341768230318719e-05</v>
       </c>
       <c r="L19" t="n">
-        <v>0.003285260533225714</v>
+        <v>0.004178638278363877</v>
       </c>
       <c r="M19" t="n">
-        <v>0.009554506702839452</v>
+        <v>0.01341435140786165</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000136690559328</v>
+        <v>1.00026943954719</v>
       </c>
       <c r="O19" t="n">
-        <v>0.009961261833734809</v>
+        <v>0.01398542811882984</v>
       </c>
       <c r="P19" t="n">
-        <v>120.6029693189826</v>
+        <v>119.2457205782022</v>
       </c>
       <c r="Q19" t="n">
-        <v>182.7656363872609</v>
+        <v>181.4083876464804</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_16_6_18</t>
+          <t>model_16_6_5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9998497650281768</v>
+        <v>0.9996968805094114</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6550398192350571</v>
+        <v>0.6440890151240956</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9998603761001821</v>
+        <v>0.9999319752765347</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9993785034303515</v>
+        <v>0.9999285009628428</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9998215121958345</v>
+        <v>0.9999299379995111</v>
       </c>
       <c r="G20" t="n">
-        <v>8.918596908713124e-05</v>
+        <v>0.0001799448236935998</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2047832648059701</v>
+        <v>0.2112841351763431</v>
       </c>
       <c r="I20" t="n">
-        <v>6.901487037212549e-05</v>
+        <v>1.712181559257334e-05</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0001842555508119059</v>
+        <v>8.971354901380105e-05</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0001266358420700278</v>
+        <v>5.341768230318719e-05</v>
       </c>
       <c r="L20" t="n">
-        <v>0.003288345918913979</v>
+        <v>0.004178638278363877</v>
       </c>
       <c r="M20" t="n">
-        <v>0.009443832330528283</v>
+        <v>0.01341435140786165</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000133542197176</v>
+        <v>1.00026943954719</v>
       </c>
       <c r="O20" t="n">
-        <v>0.009845875824266818</v>
+        <v>0.01398542811882984</v>
       </c>
       <c r="P20" t="n">
-        <v>120.6495736559606</v>
+        <v>119.2457205782022</v>
       </c>
       <c r="Q20" t="n">
-        <v>182.8122407242388</v>
+        <v>181.4083876464804</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_16_6_19</t>
+          <t>model_16_6_4</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9998524085007466</v>
+        <v>0.9996968805094114</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6548820051770136</v>
+        <v>0.6440890151240956</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9998490093489427</v>
+        <v>0.9999319752765347</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9993305379097837</v>
+        <v>0.9999285009628428</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9998075281074102</v>
+        <v>0.9999299379995111</v>
       </c>
       <c r="G21" t="n">
-        <v>8.761668957756024e-05</v>
+        <v>0.0001799448236935998</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2048769500480372</v>
+        <v>0.2112841351763431</v>
       </c>
       <c r="I21" t="n">
-        <v>7.463335592048276e-05</v>
+        <v>1.712181559257334e-05</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0001984759244130093</v>
+        <v>8.971354901380105e-05</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0001365574544819011</v>
+        <v>5.341768230318719e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>0.003291185850172653</v>
+        <v>0.004178638278363877</v>
       </c>
       <c r="M21" t="n">
-        <v>0.009360378709088657</v>
+        <v>0.01341435140786165</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000131192443781</v>
+        <v>1.00026943954719</v>
       </c>
       <c r="O21" t="n">
-        <v>0.009758869409389697</v>
+        <v>0.01398542811882984</v>
       </c>
       <c r="P21" t="n">
-        <v>120.6850781157537</v>
+        <v>119.2457205782022</v>
       </c>
       <c r="Q21" t="n">
-        <v>182.8477451840319</v>
+        <v>181.4083876464804</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_16_6_20</t>
+          <t>model_16_6_3</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9998542742065585</v>
+        <v>0.9996968805094114</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6547305251667015</v>
+        <v>0.6440890151240956</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9998375443123629</v>
+        <v>0.9999319752765347</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9992827222601226</v>
+        <v>0.9999285009628428</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9997935461038944</v>
+        <v>0.9999299379995111</v>
       </c>
       <c r="G22" t="n">
-        <v>8.650912601338829e-05</v>
+        <v>0.0001799448236935998</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2049668751257541</v>
+        <v>0.2112841351763431</v>
       </c>
       <c r="I22" t="n">
-        <v>8.030042305152105e-05</v>
+        <v>1.712181559257334e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0002126518656747663</v>
+        <v>8.971354901380105e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0001464775876660302</v>
+        <v>5.341768230318719e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>0.003293746902561792</v>
+        <v>0.004178638278363877</v>
       </c>
       <c r="M22" t="n">
-        <v>0.009301028223448646</v>
+        <v>0.01341435140786165</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000129534038615</v>
+        <v>1.00026943954719</v>
       </c>
       <c r="O22" t="n">
-        <v>0.009696992250703548</v>
+        <v>0.01398542811882984</v>
       </c>
       <c r="P22" t="n">
-        <v>120.7105212930931</v>
+        <v>119.2457205782022</v>
       </c>
       <c r="Q22" t="n">
-        <v>182.8731883613713</v>
+        <v>181.4083876464804</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_16_6_21</t>
+          <t>model_16_6_2</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9998554538376202</v>
+        <v>0.9996968805094114</v>
       </c>
       <c r="C23" t="n">
-        <v>0.654585251812932</v>
+        <v>0.6440890151240956</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9998260235454767</v>
+        <v>0.9999319752765347</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9992352337356319</v>
+        <v>0.9999285009628428</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9997796152184191</v>
+        <v>0.9999299379995111</v>
       </c>
       <c r="G23" t="n">
-        <v>8.580884605772848e-05</v>
+        <v>0.0001799448236935998</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2050531156640338</v>
+        <v>0.2112841351763431</v>
       </c>
       <c r="I23" t="n">
-        <v>8.599503718476886e-05</v>
+        <v>1.712181559257334e-05</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0002267308238936707</v>
+        <v>8.971354901380105e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0001563614529597517</v>
+        <v>5.341768230318719e-05</v>
       </c>
       <c r="L23" t="n">
-        <v>0.003296305621193472</v>
+        <v>0.004178638278363877</v>
       </c>
       <c r="M23" t="n">
-        <v>0.009263306432248071</v>
+        <v>0.01341435140786165</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000128485477671</v>
+        <v>1.00026943954719</v>
       </c>
       <c r="O23" t="n">
-        <v>0.009657664564756691</v>
+        <v>0.01398542811882984</v>
       </c>
       <c r="P23" t="n">
-        <v>120.7267769117579</v>
+        <v>119.2457205782022</v>
       </c>
       <c r="Q23" t="n">
-        <v>182.8894439800362</v>
+        <v>181.4083876464804</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_16_6_22</t>
+          <t>model_16_6_1</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9998560574740963</v>
+        <v>0.9996968805094114</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6544461525381597</v>
+        <v>0.6440890151240956</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9998145397040703</v>
+        <v>0.9999319752765347</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9991884138181159</v>
+        <v>0.9999285009628428</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9997658295407301</v>
+        <v>0.9999299379995111</v>
       </c>
       <c r="G24" t="n">
-        <v>8.545050136974224e-05</v>
+        <v>0.0001799448236935998</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2051356910023144</v>
+        <v>0.2112841351763431</v>
       </c>
       <c r="I24" t="n">
-        <v>9.167139937682792e-05</v>
+        <v>1.712181559257334e-05</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0002406115597049063</v>
+        <v>8.971354901380105e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>0.000166142294350021</v>
+        <v>5.341768230318719e-05</v>
       </c>
       <c r="L24" t="n">
-        <v>0.003298489537439583</v>
+        <v>0.004178638278363877</v>
       </c>
       <c r="M24" t="n">
-        <v>0.009243944037570881</v>
+        <v>0.01341435140786165</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000127948911914</v>
+        <v>1.00026943954719</v>
       </c>
       <c r="O24" t="n">
-        <v>0.00963747787285241</v>
+        <v>0.01398542811882984</v>
       </c>
       <c r="P24" t="n">
-        <v>120.7351465620301</v>
+        <v>119.2457205782022</v>
       </c>
       <c r="Q24" t="n">
-        <v>182.8978136303084</v>
+        <v>181.4083876464804</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_16_6_23</t>
+          <t>model_16_6_11</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9998561549444601</v>
+        <v>0.9996968805094114</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6543128861182436</v>
+        <v>0.6440890151240956</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9998031427126881</v>
+        <v>0.9999319752765347</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9991422610471667</v>
+        <v>0.9999285009628428</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9997522178838222</v>
+        <v>0.9999299379995111</v>
       </c>
       <c r="G25" t="n">
-        <v>8.539263875132279e-05</v>
+        <v>0.0001799448236935998</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2052148037059862</v>
+        <v>0.2112841351763431</v>
       </c>
       <c r="I25" t="n">
-        <v>9.730483236289564e-05</v>
+        <v>1.712181559257334e-05</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0002542945060766724</v>
+        <v>8.971354901380105e-05</v>
       </c>
       <c r="K25" t="n">
-        <v>0.000175799669219784</v>
+        <v>5.341768230318719e-05</v>
       </c>
       <c r="L25" t="n">
-        <v>0.003300499297096437</v>
+        <v>0.004178638278363877</v>
       </c>
       <c r="M25" t="n">
-        <v>0.00924081374941205</v>
+        <v>0.01341435140786165</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000127862271591</v>
+        <v>1.00026943954719</v>
       </c>
       <c r="O25" t="n">
-        <v>0.009634214321846069</v>
+        <v>0.01398542811882984</v>
       </c>
       <c r="P25" t="n">
-        <v>120.7365013163525</v>
+        <v>119.2457205782022</v>
       </c>
       <c r="Q25" t="n">
-        <v>182.8991683846307</v>
+        <v>181.4083876464804</v>
       </c>
     </row>
     <row r="26">
@@ -1837,52 +1837,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9998558172053893</v>
+        <v>0.9996968805094114</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6541852717252887</v>
+        <v>0.6440890151240956</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9997918657558976</v>
+        <v>0.9999319752765347</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9990969412087637</v>
+        <v>0.9999285009628428</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9997388198992953</v>
+        <v>0.9999299379995111</v>
       </c>
       <c r="G26" t="n">
-        <v>8.559313525334358e-05</v>
+        <v>0.0001799448236935998</v>
       </c>
       <c r="H26" t="n">
-        <v>0.205290561122299</v>
+        <v>0.2112841351763431</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0001028789333019263</v>
+        <v>1.712181559257334e-05</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0002677305123162201</v>
+        <v>8.971354901380105e-05</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0001853054450376035</v>
+        <v>5.341768230318719e-05</v>
       </c>
       <c r="L26" t="n">
-        <v>0.00330229692126206</v>
+        <v>0.004178638278363877</v>
       </c>
       <c r="M26" t="n">
-        <v>0.009251655811439571</v>
+        <v>0.01341435140786165</v>
       </c>
       <c r="N26" t="n">
-        <v>1.000128162484098</v>
+        <v>1.00026943954719</v>
       </c>
       <c r="O26" t="n">
-        <v>0.009645517952900263</v>
+        <v>0.01398542811882984</v>
       </c>
       <c r="P26" t="n">
-        <v>120.7318109473419</v>
+        <v>119.2457205782022</v>
       </c>
       <c r="Q26" t="n">
-        <v>182.8944780156201</v>
+        <v>181.4083876464804</v>
       </c>
     </row>
   </sheetData>
